--- a/projeto/entregaveis/Orcamento_Projeto_Interno_PTL.xlsx
+++ b/projeto/entregaveis/Orcamento_Projeto_Interno_PTL.xlsx
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">Projeto!E24</f>
-        <v>222482.887797295</v>
+        <v>243796.627979754</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>6</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">B5+B6</f>
-        <v>304755.492030424</v>
+        <v>326069.232212883</v>
       </c>
       <c r="C7" s="6"/>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">B7*Premissas!$B$9</f>
-        <v>30475.5492030424</v>
+        <v>32606.9232212883</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>11</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">B7+B8</f>
-        <v>335231.041233466</v>
+        <v>358676.155434171</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>13</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">B9/COUNT(Estações!$C$5:$C$44)</f>
-        <v>8380.77603083666</v>
+        <v>8966.90388585428</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B13" s="5" t="n">
         <f aca="false">'RFID futuro'!E13</f>
-        <v>36343.771811861</v>
+        <v>31918.4894118609</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>17</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B16" s="14" t="n">
         <f aca="false">'RFID futuro'!B30</f>
-        <v>2.23324417197317</v>
+        <v>1.96132038320697</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>22</v>
@@ -1668,7 +1668,7 @@
         <v>51</v>
       </c>
       <c r="B13" s="23" t="n">
-        <v>2.87</v>
+        <v>2.3804</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>52</v>
@@ -1710,7 +1710,7 @@
         <v>60</v>
       </c>
       <c r="B16" s="23" t="n">
-        <v>127.54</v>
+        <v>113.097</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>52</v>
@@ -1724,7 +1724,7 @@
         <v>61</v>
       </c>
       <c r="B17" s="23" t="n">
-        <v>35</v>
+        <v>27.4</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>52</v>
@@ -3057,11 +3057,11 @@
         <v>1408</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>45.1417049180328</v>
+        <v>55.2250459016394</v>
       </c>
       <c r="E6" s="31" t="n">
         <f aca="false">C6*D6</f>
-        <v>63559.5205245902</v>
+        <v>77756.8646295083</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3075,11 +3075,11 @@
         <v>440</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>96.8</v>
+        <v>117.59</v>
       </c>
       <c r="E7" s="31" t="n">
         <f aca="false">C7*D7</f>
-        <v>42592</v>
+        <v>51739.6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3093,11 +3093,11 @@
         <v>277</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>134.95</v>
+        <v>151.48</v>
       </c>
       <c r="E8" s="31" t="n">
         <f aca="false">C8*D8</f>
-        <v>37381.15</v>
+        <v>41959.96</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3111,11 +3111,11 @@
         <v>44</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>549.810425</v>
+        <v>673.739525</v>
       </c>
       <c r="E9" s="31" t="n">
         <f aca="false">C9*D9</f>
-        <v>24191.6587</v>
+        <v>29644.5391</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3129,11 +3129,11 @@
         <v>2433</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>4.03085245901639</v>
+        <v>2.62262295081967</v>
       </c>
       <c r="E10" s="31" t="n">
         <f aca="false">C10*D10</f>
-        <v>9807.06403278688</v>
+        <v>6380.84163934426</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3147,11 +3147,11 @@
         <v>1462</v>
       </c>
       <c r="D11" s="23" t="n">
-        <v>0.8</v>
+        <v>0.7099</v>
       </c>
       <c r="E11" s="31" t="n">
         <f aca="false">C11*D11</f>
-        <v>1169.6</v>
+        <v>1037.8738</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3165,11 +3165,11 @@
         <v>1080</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>9</v>
+        <v>4.36</v>
       </c>
       <c r="E12" s="31" t="n">
         <f aca="false">C12*D12</f>
-        <v>9720</v>
+        <v>4708.8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3183,11 +3183,11 @@
         <v>40</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>40</v>
+        <v>28.52</v>
       </c>
       <c r="E13" s="31" t="n">
         <f aca="false">C13*D13</f>
-        <v>1600</v>
+        <v>1140.8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3201,11 +3201,11 @@
         <v>40</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>45</v>
+        <v>25.611</v>
       </c>
       <c r="E14" s="31" t="n">
         <f aca="false">C14*D14</f>
-        <v>1800</v>
+        <v>1024.44</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3219,11 +3219,11 @@
         <v>2000</v>
       </c>
       <c r="D15" s="23" t="n">
-        <v>4.03085245901639</v>
+        <v>2.62262295081967</v>
       </c>
       <c r="E15" s="31" t="n">
         <f aca="false">C15*D15</f>
-        <v>8061.70491803278</v>
+        <v>5245.24590163934</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3273,11 +3273,11 @@
         <v>2</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>550</v>
+        <v>431.08</v>
       </c>
       <c r="E18" s="31" t="n">
         <f aca="false">C18*D18</f>
-        <v>1100</v>
+        <v>862.16</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3291,11 +3291,11 @@
         <v>160</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>4.03085245901639</v>
+        <v>2.62262295081967</v>
       </c>
       <c r="E19" s="31" t="n">
         <f aca="false">C19*D19</f>
-        <v>644.936393442622</v>
+        <v>419.619672131147</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3345,11 +3345,11 @@
         <v>1</v>
       </c>
       <c r="D22" s="23" t="n">
-        <v>700</v>
+        <v>705.69</v>
       </c>
       <c r="E22" s="31" t="n">
         <f aca="false">C22*D22</f>
-        <v>700</v>
+        <v>705.69</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="E23" s="31" t="n">
         <f aca="false">SUM(E6:E22)*D23</f>
-        <v>10594.4232284426</v>
+        <v>11609.3632371312</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3378,7 +3378,7 @@
       <c r="D24" s="29"/>
       <c r="E24" s="10" t="n">
         <f aca="false">SUM(E6:E23)</f>
-        <v>222482.887797295</v>
+        <v>243796.627979754</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3566,7 +3566,7 @@
       <c r="D37" s="29"/>
       <c r="E37" s="10" t="n">
         <f aca="false">E24+E35</f>
-        <v>304755.492030424</v>
+        <v>326069.232212883</v>
       </c>
     </row>
   </sheetData>
@@ -3658,11 +3658,11 @@
       </c>
       <c r="D6" s="5" t="n">
         <f aca="false">Premissas!$B$13</f>
-        <v>2.87</v>
+        <v>2.3804</v>
       </c>
       <c r="E6" s="31" t="n">
         <f aca="false">C6*D6</f>
-        <v>14350</v>
+        <v>11902</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3698,11 +3698,11 @@
       </c>
       <c r="D8" s="5" t="n">
         <f aca="false">Premissas!$B$16</f>
-        <v>127.54</v>
+        <v>113.097</v>
       </c>
       <c r="E8" s="31" t="n">
         <f aca="false">C8*D8</f>
-        <v>11223.52</v>
+        <v>9952.536</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3718,11 +3718,11 @@
       </c>
       <c r="D9" s="5" t="n">
         <f aca="false">Premissas!$B$17</f>
-        <v>35</v>
+        <v>27.4</v>
       </c>
       <c r="E9" s="31" t="n">
         <f aca="false">C9*D9</f>
-        <v>1400</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3754,7 +3754,7 @@
       <c r="D11" s="29"/>
       <c r="E11" s="10" t="n">
         <f aca="false">SUM(E6:E10)</f>
-        <v>33039.7925562372</v>
+        <v>29016.8085562372</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="E12" s="31" t="n">
         <f aca="false">E11*D12</f>
-        <v>3303.97925562372</v>
+        <v>2901.68085562372</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3783,7 +3783,7 @@
       <c r="D13" s="29"/>
       <c r="E13" s="10" t="n">
         <f aca="false">E11+E12</f>
-        <v>36343.771811861</v>
+        <v>31918.4894118609</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="G17" s="31" t="n">
         <f aca="false">(C17*Premissas!$B$13+D17*Premissas!$B$16+E17*Premissas!$B$17+F17*Premissas!$B$6)*(1+Premissas!$B$9)</f>
-        <v>1935.94623721881</v>
+        <v>1705.14973721881</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="G18" s="31" t="n">
         <f aca="false">(C18*Premissas!$B$13+D18*Premissas!$B$16+E18*Premissas!$B$17+F18*Premissas!$B$6)*(1+Premissas!$B$9)</f>
-        <v>17302.8774928425</v>
+        <v>15197.6908928425</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="G19" s="31" t="n">
         <f aca="false">(C19*Premissas!$B$13+D19*Premissas!$B$16+E19*Premissas!$B$17+F19*Premissas!$B$6)*(1+Premissas!$B$9)</f>
-        <v>17302.8774928425</v>
+        <v>15197.6908928425</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G20" s="10" t="n">
         <f aca="false">SUM(G17:G19)</f>
-        <v>36541.7012229039</v>
+        <v>32100.5315229039</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="B30" s="38" t="n">
         <f aca="false">IF(B29&gt;0,E13/B29,0)</f>
-        <v>2.23324417197317</v>
+        <v>1.96132038320697</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>230</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C33" s="31" t="n">
         <f aca="false">SUM($G$17:G17)</f>
-        <v>1935.94623721881</v>
+        <v>1705.14973721881</v>
       </c>
       <c r="D33" s="31" t="n">
         <f aca="false">$B$29*B33/COUNT(Estações!$C$5:$C$44)</f>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="F33" s="35" t="n">
         <f aca="false">IF(D33&gt;0,G17/D33,0)</f>
-        <v>2.37919205188897</v>
+        <v>2.09555339093492</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="C34" s="31" t="n">
         <f aca="false">SUM($G$17:G18)</f>
-        <v>19238.8237300614</v>
+        <v>16902.8406300614</v>
       </c>
       <c r="D34" s="31" t="n">
         <f aca="false">$B$29*B34/COUNT(Estações!$C$5:$C$44)</f>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="F34" s="35" t="n">
         <f aca="false">IF(D34&gt;0,G18/D34,0)</f>
-        <v>2.23836515021583</v>
+        <v>1.96603031330269</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="C35" s="31" t="n">
         <f aca="false">SUM($G$17:G19)</f>
-        <v>36541.7012229039</v>
+        <v>32100.5315229039</v>
       </c>
       <c r="D35" s="31" t="n">
         <f aca="false">$B$29*B35/COUNT(Estações!$C$5:$C$44)</f>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="F35" s="35" t="n">
         <f aca="false">IF(D35&gt;0,G19/D35,0)</f>
-        <v>2.23836515021583</v>
+        <v>1.96603031330269</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/projeto/entregaveis/Orcamento_Projeto_Interno_PTL.xlsx
+++ b/projeto/entregaveis/Orcamento_Projeto_Interno_PTL.xlsx
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">Projeto!E24</f>
-        <v>243796.627979754</v>
+        <v>223030.137479754</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>6</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">B5+B6</f>
-        <v>326069.232212883</v>
+        <v>305302.741712883</v>
       </c>
       <c r="C7" s="6"/>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">B7*Premissas!$B$9</f>
-        <v>32606.9232212883</v>
+        <v>30530.2741712883</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>11</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">B7+B8</f>
-        <v>358676.155434171</v>
+        <v>335833.015884171</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>13</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">B9/COUNT(Estações!$C$5:$C$44)</f>
-        <v>8966.90388585428</v>
+        <v>8395.82539710428</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -3057,11 +3057,11 @@
         <v>1408</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>55.2250459016394</v>
+        <v>47.8850459016393</v>
       </c>
       <c r="E6" s="31" t="n">
         <f aca="false">C6*D6</f>
-        <v>77756.8646295083</v>
+        <v>67422.1446295081</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3075,11 +3075,11 @@
         <v>440</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>117.59</v>
+        <v>104.42</v>
       </c>
       <c r="E7" s="31" t="n">
         <f aca="false">C7*D7</f>
-        <v>51739.6</v>
+        <v>45944.8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3093,11 +3093,11 @@
         <v>277</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>151.48</v>
+        <v>138.31</v>
       </c>
       <c r="E8" s="31" t="n">
         <f aca="false">C8*D8</f>
-        <v>41959.96</v>
+        <v>38311.87</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="E23" s="31" t="n">
         <f aca="false">SUM(E6:E22)*D23</f>
-        <v>11609.3632371312</v>
+        <v>10620.4827371311</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3378,7 +3378,7 @@
       <c r="D24" s="29"/>
       <c r="E24" s="10" t="n">
         <f aca="false">SUM(E6:E23)</f>
-        <v>243796.627979754</v>
+        <v>223030.137479754</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3566,7 +3566,7 @@
       <c r="D37" s="29"/>
       <c r="E37" s="10" t="n">
         <f aca="false">E24+E35</f>
-        <v>326069.232212883</v>
+        <v>305302.741712883</v>
       </c>
     </row>
   </sheetData>
